--- a/data/processed/06_full_TOPNUM.xlsx
+++ b/data/processed/06_full_TOPNUM.xlsx
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>feature</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>cluster</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -456,456 +456,456 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_group</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>0.1029624187676733</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1029624187676733</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>living_area</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.08816554930453399</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08816554930453399</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.062206575386208</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.062206575386208</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.06109782006988426</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.06109782006988426</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0582925153076121</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0582925153076121</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>housing_status</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04065041158368955</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04065041158368955</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>political_preference</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.0237346282182135</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0237346282182135</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.005186071808534137</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.005186071808534137</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2302292822926965</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2302292822926965</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>living_area</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.1444115581111836</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1444115581111836</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>political_preference</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.1360373692144417</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1360373692144417</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>age_group</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.1030135294279408</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.1030135294279408</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.1179491312607334</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1179491312607334</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.1175917815312772</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1175917815312772</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1119767478024273</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.1119767478024273</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>housing_status</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.07423240514039588</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.07423240514039588</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.06105658676540291</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.06105658676540291</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>age_group</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.1660531661860283</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1660531661860283</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.1068981861596944</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1068981861596944</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>political_preference</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.09551424358356586</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.09551424358356586</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>living_area</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.08820931478218826</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.08820931478218826</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="B21" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C21" t="n">
+        <v>-0.08882755667911701</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.08882755667911701</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.05938246264419426</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.05938246264419426</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>education</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>-0.06223745480006623</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.06223745480006623</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.05027761063868636</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05027761063868636</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>kids</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.06112814909635872</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.06112814909635872</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.05832145177765317</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.05832145177765317</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.04002643332891577</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.04002643332891577</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>housing_status</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0.04067059049363608</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.04067059049363608</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>political_preference</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.02374641011430682</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.02374641011430682</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>net_income</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.005188646180402062</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.005188646180402062</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.2303435683668946</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2303435683668946</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>living_area</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.1444832441707543</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.1444832441707543</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>political_preference</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.1361048983172428</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.1361048983172428</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.1180076813419074</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.1180076813419074</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.1176501542236443</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.1176501542236443</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>education</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1120323331857476</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.1120323331857476</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>housing_status</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.07426925418964495</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.07426925418964495</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>net_income</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.06108689532361873</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.06108689532361873</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>age_group</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.1661355951641435</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1661355951641435</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>gender</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.1069512505393139</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1069512505393139</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>political_preference</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.09556165696131028</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.09556165696131028</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>living_area</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.08887165077797522</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.08887165077797522</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>net_income</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.05941194016531685</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.05941194016531685</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>education</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.05030256850105181</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.05030256850105181</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.04004630249535612</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.04004630249535612</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>housing_status</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.03156978384141972</v>
+        <v>-0.03155412034065822</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03156978384141972</v>
+        <v>0.03155412034065822</v>
       </c>
       <c r="E25" t="n">
         <v>-1</v>
